--- a/data/raw/관세청/Import Export Performance by Commodity and Country(GW)/Soybean Oil/1507.10/Food use (.1000)/U.S.A.xlsx
+++ b/data/raw/관세청/Import Export Performance by Commodity and Country(GW)/Soybean Oil/1507.10/Food use (.1000)/U.S.A.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\데이터플랫폼팀\00 데이터플랫폼팀_공유\데이터플랫폼팀(23.03~)\08 데이터 분석\00 분석과제정의서\☆구매\수입원료\대두유\데이터\외부\경제, 무역\관세청\9개년_품목별 국가별 수출입실적\대두유\1507.10\식품용(.1000)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\데이터플랫폼팀\00 데이터플랫폼팀_공유\데이터플랫폼팀(23.03~)\08 데이터 분석\00 분석과제정의서\☆구매\수입원료\대두유\데이터\외부\경제, 무역\관세청\15개년_품목별 국가별 수출입실적\대두유\1507.10\식품용(.1000)\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -1721,10 +1721,10 @@
       </c>
       <c r="B4" s="2">
         <f t="shared" si="0"/>
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="C4" s="2">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="D4" s="2">
         <v>3</v>
@@ -1952,11 +1952,11 @@
       </c>
       <c r="B15" s="5">
         <f>SUM(B3:B14)</f>
-        <v>-168347743</v>
+        <v>-168347723</v>
       </c>
       <c r="C15" s="5">
         <f t="shared" ref="C15:F15" si="1">SUM(C3:C14)</f>
-        <v>7737</v>
+        <v>7757</v>
       </c>
       <c r="D15" s="5">
         <f t="shared" si="1"/>
@@ -1975,6 +1975,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2054,20 +2055,12 @@
       </c>
       <c r="B5" s="2">
         <f t="shared" si="0"/>
-        <v>-158</v>
-      </c>
-      <c r="C5" s="2">
-        <v>0</v>
-      </c>
-      <c r="D5" s="2">
-        <v>0</v>
-      </c>
-      <c r="E5" s="2">
-        <v>158</v>
-      </c>
-      <c r="F5" s="2">
-        <v>1E-3</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
@@ -2075,20 +2068,12 @@
       </c>
       <c r="B6" s="2">
         <f t="shared" si="0"/>
-        <v>-453</v>
-      </c>
-      <c r="C6" s="2">
-        <v>0</v>
-      </c>
-      <c r="D6" s="2">
-        <v>0</v>
-      </c>
-      <c r="E6" s="2">
-        <v>453</v>
-      </c>
-      <c r="F6" s="2">
-        <v>3.0000000000000001E-3</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
@@ -2098,18 +2083,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C7" s="2">
-        <v>0</v>
-      </c>
-      <c r="D7" s="2">
-        <v>0</v>
-      </c>
-      <c r="E7" s="2">
-        <v>0</v>
-      </c>
-      <c r="F7" s="2">
-        <v>0</v>
-      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
@@ -2119,18 +2096,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C8" s="2">
-        <v>0</v>
-      </c>
-      <c r="D8" s="2">
-        <v>0</v>
-      </c>
-      <c r="E8" s="2">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2">
-        <v>0</v>
-      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
@@ -2140,18 +2109,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C9" s="2">
-        <v>0</v>
-      </c>
-      <c r="D9" s="2">
-        <v>0</v>
-      </c>
-      <c r="E9" s="2">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2">
-        <v>0</v>
-      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
@@ -2159,20 +2120,12 @@
       </c>
       <c r="B10" s="2">
         <f t="shared" si="0"/>
-        <v>-16</v>
-      </c>
-      <c r="C10" s="2">
-        <v>0</v>
-      </c>
-      <c r="D10" s="2">
-        <v>0</v>
-      </c>
-      <c r="E10" s="2">
-        <v>16</v>
-      </c>
-      <c r="F10" s="2">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
@@ -2182,18 +2135,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C11" s="2">
-        <v>0</v>
-      </c>
-      <c r="D11" s="2">
-        <v>0</v>
-      </c>
-      <c r="E11" s="2">
-        <v>0</v>
-      </c>
-      <c r="F11" s="2">
-        <v>0</v>
-      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
@@ -2203,18 +2148,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C12" s="2">
-        <v>0</v>
-      </c>
-      <c r="D12" s="2">
-        <v>0</v>
-      </c>
-      <c r="E12" s="2">
-        <v>0</v>
-      </c>
-      <c r="F12" s="2">
-        <v>0</v>
-      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
@@ -2224,18 +2161,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C13" s="2">
-        <v>0</v>
-      </c>
-      <c r="D13" s="2">
-        <v>0</v>
-      </c>
-      <c r="E13" s="2">
-        <v>0</v>
-      </c>
-      <c r="F13" s="2">
-        <v>0</v>
-      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
@@ -2245,18 +2174,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C14" s="2">
-        <v>0</v>
-      </c>
-      <c r="D14" s="2">
-        <v>0</v>
-      </c>
-      <c r="E14" s="2">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2">
-        <v>0</v>
-      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
     </row>
     <row r="15" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
@@ -2264,7 +2185,7 @@
       </c>
       <c r="B15" s="5">
         <f>SUM(B3:B14)</f>
-        <v>1007</v>
+        <v>1634</v>
       </c>
       <c r="C15" s="5">
         <f t="shared" ref="C15:F15" si="1">SUM(C3:C14)</f>
@@ -2276,11 +2197,11 @@
       </c>
       <c r="E15" s="5">
         <f t="shared" si="1"/>
-        <v>627</v>
+        <v>0</v>
       </c>
       <c r="F15" s="5">
         <f t="shared" si="1"/>
-        <v>1.004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
@@ -2326,18 +2247,10 @@
         <f t="shared" ref="B3:B14" si="0">C3-E3</f>
         <v>0</v>
       </c>
-      <c r="C3" s="2">
-        <v>0</v>
-      </c>
-      <c r="D3" s="2">
-        <v>0</v>
-      </c>
-      <c r="E3" s="2">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2">
-        <v>0</v>
-      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -2347,18 +2260,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C4" s="2">
-        <v>0</v>
-      </c>
-      <c r="D4" s="2">
-        <v>0</v>
-      </c>
-      <c r="E4" s="2">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2">
-        <v>0</v>
-      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
@@ -2368,18 +2273,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C5" s="2">
-        <v>0</v>
-      </c>
-      <c r="D5" s="2">
-        <v>0</v>
-      </c>
-      <c r="E5" s="2">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2">
-        <v>0</v>
-      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
@@ -2389,18 +2286,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C6" s="2">
-        <v>0</v>
-      </c>
-      <c r="D6" s="2">
-        <v>0</v>
-      </c>
-      <c r="E6" s="2">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2">
-        <v>0</v>
-      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
@@ -2452,18 +2341,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C9" s="2">
-        <v>0</v>
-      </c>
-      <c r="D9" s="2">
-        <v>0</v>
-      </c>
-      <c r="E9" s="2">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2">
-        <v>0</v>
-      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
@@ -2494,18 +2375,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C11" s="2">
-        <v>0</v>
-      </c>
-      <c r="D11" s="2">
-        <v>0</v>
-      </c>
-      <c r="E11" s="2">
-        <v>0</v>
-      </c>
-      <c r="F11" s="2">
-        <v>0</v>
-      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
@@ -2515,18 +2388,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C12" s="2">
-        <v>0</v>
-      </c>
-      <c r="D12" s="2">
-        <v>0</v>
-      </c>
-      <c r="E12" s="2">
-        <v>0</v>
-      </c>
-      <c r="F12" s="2">
-        <v>0</v>
-      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
@@ -2536,18 +2401,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C13" s="2">
-        <v>0</v>
-      </c>
-      <c r="D13" s="2">
-        <v>0</v>
-      </c>
-      <c r="E13" s="2">
-        <v>0</v>
-      </c>
-      <c r="F13" s="2">
-        <v>0</v>
-      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
@@ -2659,18 +2516,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C4" s="2">
-        <v>0</v>
-      </c>
-      <c r="D4" s="2">
-        <v>0</v>
-      </c>
-      <c r="E4" s="2">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2">
-        <v>0</v>
-      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
@@ -2764,18 +2613,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C9" s="2">
-        <v>0</v>
-      </c>
-      <c r="D9" s="2">
-        <v>0</v>
-      </c>
-      <c r="E9" s="2">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2">
-        <v>0</v>
-      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
@@ -2785,18 +2626,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C10" s="2">
-        <v>0</v>
-      </c>
-      <c r="D10" s="2">
-        <v>0</v>
-      </c>
-      <c r="E10" s="2">
-        <v>0</v>
-      </c>
-      <c r="F10" s="2">
-        <v>0</v>
-      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
@@ -2806,18 +2639,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C11" s="2">
-        <v>0</v>
-      </c>
-      <c r="D11" s="2">
-        <v>0</v>
-      </c>
-      <c r="E11" s="2">
-        <v>0</v>
-      </c>
-      <c r="F11" s="2">
-        <v>0</v>
-      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
@@ -2827,18 +2652,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C12" s="2">
-        <v>0</v>
-      </c>
-      <c r="D12" s="2">
-        <v>0</v>
-      </c>
-      <c r="E12" s="2">
-        <v>0</v>
-      </c>
-      <c r="F12" s="2">
-        <v>0</v>
-      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
@@ -2848,18 +2665,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C13" s="2">
-        <v>0</v>
-      </c>
-      <c r="D13" s="2">
-        <v>0</v>
-      </c>
-      <c r="E13" s="2">
-        <v>0</v>
-      </c>
-      <c r="F13" s="2">
-        <v>0</v>
-      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
@@ -2869,18 +2678,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C14" s="2">
-        <v>0</v>
-      </c>
-      <c r="D14" s="2">
-        <v>0</v>
-      </c>
-      <c r="E14" s="2">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2">
-        <v>0</v>
-      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
     </row>
     <row r="15" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
